--- a/artfynd/A 43725-2023 artfynd.xlsx
+++ b/artfynd/A 43725-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43725-2023 artfynd.xlsx
+++ b/artfynd/A 43725-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1853,121 +1853,6 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>114461569</v>
-      </c>
-      <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Murbäcken (1), Upl</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>624413</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6681786</v>
-      </c>
-      <c r="S12" t="n">
-        <v>25</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Heby</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Östervåla</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>C-Heb-0231</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2022-12-31</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2022-12-31</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43725-2023 artfynd.xlsx
+++ b/artfynd/A 43725-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98361398</v>
+        <v>98361403</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624461.0202838875</v>
+        <v>624537</v>
       </c>
       <c r="R2" t="n">
-        <v>6681791.203117763</v>
+        <v>6681804</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -752,19 +747,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98361403</v>
+        <v>98361404</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624537.2063204317</v>
+        <v>624548</v>
       </c>
       <c r="R3" t="n">
-        <v>6681804.233889947</v>
+        <v>6681727</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -872,19 +852,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,37 +885,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98361399</v>
+        <v>98361406</v>
       </c>
       <c r="B4" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624451.0290688516</v>
+        <v>624619</v>
       </c>
       <c r="R4" t="n">
-        <v>6681792.352796886</v>
+        <v>6681734</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -992,19 +957,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,37 +990,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98361397</v>
+        <v>98361396</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1079,13 +1029,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624498.4769387683</v>
+        <v>624457</v>
       </c>
       <c r="R5" t="n">
-        <v>6681772.609313298</v>
+        <v>6681742</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,19 +1062,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,15 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98361404</v>
+        <v>98361405</v>
       </c>
       <c r="B6" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1199,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624547.782845789</v>
+        <v>624611</v>
       </c>
       <c r="R6" t="n">
-        <v>6681727.593678902</v>
+        <v>6681726</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1232,19 +1167,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,15 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98361396</v>
+        <v>103870721</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,24 +1228,20 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Utvidgning Låghällsmossens NR, Upl</t>
+          <t>norr Långhällsjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624456.713959316</v>
+        <v>624614</v>
       </c>
       <c r="R7" t="n">
-        <v>6681742.371846947</v>
+        <v>6681730</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,22 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,78 +1281,78 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>fuktig äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
-        </is>
-      </c>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105420078</v>
+        <v>98361397</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Murbäcken, Upl</t>
+          <t>Utvidgning Låghällsmossens NR, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624413.4413519108</v>
+        <v>624498</v>
       </c>
       <c r="R8" t="n">
-        <v>6681785.606944388</v>
+        <v>6681773</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1470,22 +1376,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-12-31</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-12-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,66 +1396,68 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105419811</v>
+        <v>98361398</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Murbäcken, Upl</t>
+          <t>Utvidgning Låghällsmossens NR, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624465.391976753</v>
+        <v>624461</v>
       </c>
       <c r="R9" t="n">
-        <v>6681794.332838892</v>
+        <v>6681791</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,22 +1481,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-12-31</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-12-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,27 +1501,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105420026</v>
+        <v>98361407</v>
       </c>
       <c r="B10" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,42 +1528,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Murbäcken, Upl</t>
+          <t>Utvidgning Låghällsmossens NR, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624422.5334633418</v>
+        <v>624616</v>
       </c>
       <c r="R10" t="n">
-        <v>6681767.03926772</v>
+        <v>6681741</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1700,22 +1586,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-12-31</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-12-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,27 +1606,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105420216</v>
+        <v>103870720</v>
       </c>
       <c r="B11" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,20 +1651,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Murbäcken, Upl</t>
+          <t>norr Långhällsjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624398.6931055371</v>
+        <v>624614</v>
       </c>
       <c r="R11" t="n">
-        <v>6681765.729954419</v>
+        <v>6681730</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1813,22 +1687,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-12-31</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-12-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,19 +1703,972 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>fuktig äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>105420216</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Murbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>624398</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6681765</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>105419811</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Murbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>624465</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6681794</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>98361399</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Utvidgning Låghällsmossens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>624451</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6681792</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-05-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-05-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>103870722</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4819</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100857</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Robust tickgnagare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dorcatoma robusta</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Strand, 1938</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>norr Långhällsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>624587</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6681817</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>fuktig äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>björkhögstubbe med fnöskticka</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>103870723</v>
+      </c>
+      <c r="B16" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>norr Långhällsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>624587</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6681817</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>fuktig äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>björkhögstubbe med fnöskticka</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>103870656</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>norr Långhällsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>624579</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6681838</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ca 4 kvm</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>fuktig äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>105420078</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Murbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>624413</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6681786</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>105419467</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Murbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>624618</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6681733</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>105420026</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Murbäcken, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>624423</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6681767</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Östervåla</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43725-2023 artfynd.xlsx
+++ b/artfynd/A 43725-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361403</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361404</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361406</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361396</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361405</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870721</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361397</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1514,6 +1554,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361398</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1619,6 +1664,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361407</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1726,6 +1776,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870720</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1824,6 +1879,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105420216</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1922,6 +1982,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105419811</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2027,6 +2092,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361399</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2139,6 +2209,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870722</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2251,6 +2326,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870723</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2363,6 +2443,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103870656</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2465,6 +2550,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105420078</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2567,6 +2657,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105419467</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2669,8 +2764,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105420026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>